--- a/output/Hubei/鄂州市_news.xlsx
+++ b/output/Hubei/鄂州市_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P177"/>
+  <dimension ref="A1:P178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,14 +565,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230414_542535.html</t>
@@ -639,14 +637,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="M3" t="n">
         <v>58</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230414_542534.html</t>
@@ -713,14 +709,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="M4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230414_542533.html</t>
@@ -787,14 +781,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="M5" t="n">
         <v>94</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230414_542532.html</t>
@@ -861,14 +853,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/srlzyhshbzj/202304/t20230414_542530.html</t>
@@ -935,14 +925,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="M7" t="n">
         <v>50</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230414_542526.html</t>
@@ -1009,14 +997,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230414_542525.html</t>
@@ -1083,14 +1069,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230414_542523.html</t>
@@ -1157,14 +1141,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="M10" t="n">
         <v>10</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230414_542518.html</t>
@@ -1231,14 +1213,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="M11" t="n">
-        <v>36</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230414_542515.html</t>
@@ -1305,14 +1285,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="M12" t="n">
         <v>17</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230414_542511.html</t>
@@ -1379,14 +1357,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M13" t="n">
         <v>6</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230414_542508.html</t>
@@ -1453,14 +1429,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230414_542504.html</t>
@@ -1527,14 +1501,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="M15" t="n">
-        <v>81</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230414_542501.html</t>
@@ -1601,14 +1573,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="M16" t="n">
-        <v>152</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sqxj/202304/t20230410_540252.html</t>
@@ -1675,14 +1645,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="M17" t="n">
-        <v>55</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sqxj/202304/t20230410_540251.html</t>
@@ -1749,14 +1717,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="M18" t="n">
-        <v>37</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/srlzyhshbzj/202304/t20230410_540250.html</t>
@@ -1823,14 +1789,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/srlzyhshbzj/202304/t20230410_540249.html</t>
@@ -1897,14 +1861,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="M20" t="n">
         <v>6</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/srlzyhshbzj/202304/t20230410_540245.html</t>
@@ -1971,14 +1933,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="M21" t="n">
         <v>112</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/scsglzfwyh/202304/t20230410_540241.html</t>
@@ -2045,14 +2005,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="M22" t="n">
         <v>12</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/scsglzfwyh/202304/t20230410_540240.html</t>
@@ -2119,14 +2077,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M23" t="n">
         <v>51</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/scsglzfwyh/202304/t20230410_540239.html</t>
@@ -2193,14 +2149,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="M24" t="n">
         <v>46</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/scsglzfwyh/202304/t20230410_540238.html</t>
@@ -2267,14 +2221,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M25" t="n">
         <v>36</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szsfwzx/202304/t20230410_540237.html</t>
@@ -2341,14 +2293,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="M26" t="n">
-        <v>60</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgaj/202304/t20230410_540236.html</t>
@@ -2415,14 +2365,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M27" t="n">
         <v>8</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgaj/202304/t20230410_540202.html</t>
@@ -2489,14 +2437,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M28" t="n">
         <v>7</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgaj/202304/t20230410_540201.html</t>
@@ -2563,14 +2509,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="M29" t="n">
         <v>4</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540199.html</t>
@@ -2637,14 +2581,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540198.html</t>
@@ -2711,14 +2653,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540197.html</t>
@@ -2785,14 +2725,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M32" t="n">
         <v>13</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540196.html</t>
@@ -2859,14 +2797,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540194.html</t>
@@ -2933,14 +2869,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540193.html</t>
@@ -3007,14 +2941,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="M35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sylbzj/202304/t20230410_540192.html</t>
@@ -3081,14 +3013,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/syjj/202304/t20230410_540191.html</t>
@@ -3155,14 +3085,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="M37" t="n">
         <v>2</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/syjj/202304/t20230410_540188.html</t>
@@ -3229,14 +3157,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M38" t="n">
         <v>2</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/syjj/202304/t20230410_540186.html</t>
@@ -3303,14 +3229,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="M39" t="n">
-        <v>101</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/syjj/202304/t20230410_540183.html</t>
@@ -3377,14 +3301,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="M40" t="n">
-        <v>289</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sslhhbj/202304/t20230410_540179.html</t>
@@ -3451,14 +3373,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sslhhbj/202304/t20230410_540174.html</t>
@@ -3525,14 +3445,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="M42" t="n">
         <v>10</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sslhhbj/202304/t20230410_540173.html</t>
@@ -3599,14 +3517,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M43" t="n">
         <v>28</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssfj/202304/t20230410_540168.html</t>
@@ -3673,14 +3589,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M44" t="n">
         <v>54</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssfj/202304/t20230410_540165.html</t>
@@ -3747,14 +3661,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="M45" t="n">
         <v>2</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssfj/202304/t20230410_540164.html</t>
@@ -3821,14 +3733,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="M46" t="n">
         <v>9</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssfj/202304/t20230410_540163.html</t>
@@ -3895,14 +3805,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssfj/202304/t20230410_540161.html</t>
@@ -3969,14 +3877,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M48" t="n">
-        <v>26</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540160.html</t>
@@ -4043,14 +3949,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M49" t="n">
         <v>12</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540159.html</t>
@@ -4117,14 +4021,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="M50" t="n">
         <v>8</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540158.html</t>
@@ -4191,14 +4093,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="M51" t="n">
         <v>15</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540157.html</t>
@@ -4265,14 +4165,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540156.html</t>
@@ -4339,14 +4237,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M53" t="n">
         <v>6</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sswj/202304/t20230410_540155.html</t>
@@ -4413,14 +4309,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M54" t="n">
         <v>6</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swhhlyj/202304/t20230410_540153.html</t>
@@ -4487,14 +4381,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swhhlyj/202304/t20230410_540152.html</t>
@@ -4561,14 +4453,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M56" t="n">
         <v>8</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swhhlyj/202304/t20230410_540151.html</t>
@@ -4635,14 +4525,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M57" t="n">
         <v>2</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swhhlyj/202304/t20230410_540149.html</t>
@@ -4709,14 +4597,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M58" t="n">
         <v>6</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swhhlyj/202304/t20230410_540147.html</t>
@@ -4783,14 +4669,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540146.html</t>
@@ -4857,14 +4741,12 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M60" t="n">
         <v>2</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540145.html</t>
@@ -4936,9 +4818,7 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540144.html</t>
@@ -5005,14 +4885,12 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="M62" t="n">
         <v>4</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540143.html</t>
@@ -5079,14 +4957,12 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="M63" t="n">
-        <v>61</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540142.html</t>
@@ -5153,14 +5029,12 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="M64" t="n">
         <v>21</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540140.html</t>
@@ -5227,14 +5101,12 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="M65" t="n">
         <v>19</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjyj/202304/t20230410_540139.html</t>
@@ -5301,14 +5173,12 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M66" t="n">
         <v>46</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssjj/202304/t20230410_540138.html</t>
@@ -5375,14 +5245,12 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssjj/202304/t20230410_540129.html</t>
@@ -5449,14 +5317,12 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="M68" t="n">
-        <v>6</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/snyncj/202304/t20230410_540124.html</t>
@@ -5523,14 +5389,12 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M69" t="n">
         <v>23</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/snyncj/202304/t20230410_540123.html</t>
@@ -5597,14 +5461,12 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="M70" t="n">
         <v>4</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/snyncj/202304/t20230410_540120.html</t>
@@ -5671,14 +5533,12 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M71" t="n">
         <v>5</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/snyncj/202304/t20230410_540119.html</t>
@@ -5745,14 +5605,12 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M72" t="n">
         <v>3</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sxzspj/202304/t20230410_540115.html</t>
@@ -5819,14 +5677,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>90</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sxzspj/202304/t20230410_540112.html</t>
@@ -5893,14 +5747,12 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sxzspj/202304/t20230410_540110.html</t>
@@ -5967,14 +5819,12 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="M75" t="n">
         <v>3</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sxzspj/202304/t20230410_540108.html</t>
@@ -6041,14 +5891,12 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="M76" t="n">
         <v>8</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sxzspj/202304/t20230410_540104.html</t>
@@ -6115,14 +5963,12 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="M77" t="n">
-        <v>32</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540100.html</t>
@@ -6189,14 +6035,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="M78" t="n">
         <v>28</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540099.html</t>
@@ -6263,14 +6107,12 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M79" t="n">
         <v>2</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540097.html</t>
@@ -6337,14 +6179,12 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M80" t="n">
         <v>2</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540096.html</t>
@@ -6411,14 +6251,12 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M81" t="n">
         <v>7</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540094.html</t>
@@ -6485,14 +6323,12 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="M82" t="n">
         <v>28</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540092.html</t>
@@ -6559,14 +6395,12 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="M83" t="n">
         <v>7</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540091.html</t>
@@ -6633,14 +6467,12 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="M84" t="n">
         <v>5</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540090.html</t>
@@ -6707,14 +6539,12 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="M85" t="n">
         <v>8</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540088.html</t>
@@ -6781,14 +6611,12 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540086.html</t>
@@ -6855,14 +6683,12 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="M87" t="n">
         <v>2</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/swjw/202304/t20230410_540085.html</t>
@@ -6929,14 +6755,12 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="M88" t="n">
         <v>4</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540080.html</t>
@@ -7003,14 +6827,12 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540067.html</t>
@@ -7077,14 +6899,12 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540059.html</t>
@@ -7151,14 +6971,12 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="M91" t="n">
         <v>6</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540055.html</t>
@@ -7225,14 +7043,12 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="M92" t="n">
-        <v>120</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540052.html</t>
@@ -7299,14 +7115,12 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="M93" t="n">
-        <v>17</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540037.html</t>
@@ -7373,14 +7187,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>85</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540029.html</t>
@@ -7447,14 +7257,12 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="M95" t="n">
         <v>14</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540025.html</t>
@@ -7521,14 +7329,12 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="M96" t="n">
-        <v>14</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540021.html</t>
@@ -7595,14 +7401,12 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="M97" t="n">
         <v>30</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/smzj/202304/t20230410_540016.html</t>
@@ -7669,14 +7473,12 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="M98" t="n">
         <v>6</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540011.html</t>
@@ -7743,14 +7545,12 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="M99" t="n">
         <v>7</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540010.html</t>
@@ -7817,14 +7617,12 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="M100" t="n">
         <v>9</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540008.html</t>
@@ -7891,14 +7689,12 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M101" t="n">
         <v>6</v>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540006.html</t>
@@ -7965,14 +7761,12 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="M102" t="n">
         <v>8</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540003.html</t>
@@ -8039,14 +7833,12 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="M103" t="n">
         <v>52</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540002.html</t>
@@ -8113,14 +7905,12 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M104" t="n">
         <v>2</v>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/styjrswj/202304/t20230410_540001.html</t>
@@ -8187,14 +7977,12 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="M105" t="n">
         <v>3</v>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_540000.html</t>
@@ -8261,14 +8049,12 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="M106" t="n">
         <v>4</v>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_539999.html</t>
@@ -8335,14 +8121,12 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M107" t="n">
         <v>46</v>
       </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_539998.html</t>
@@ -8409,14 +8193,12 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M108" t="n">
         <v>46</v>
       </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_539991.html</t>
@@ -8483,14 +8265,12 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M109" t="n">
         <v>65</v>
       </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_539981.html</t>
@@ -8557,14 +8337,12 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="M110" t="n">
         <v>38</v>
       </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szfgjj/202304/t20230410_539942.html</t>
@@ -8631,14 +8409,12 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="M111" t="n">
         <v>11</v>
       </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539929.html</t>
@@ -8705,14 +8481,12 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="M112" t="n">
         <v>39</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539927.html</t>
@@ -8779,14 +8553,12 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="M113" t="n">
         <v>25</v>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539925.html</t>
@@ -8853,14 +8625,12 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M114" t="n">
         <v>11</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539920.html</t>
@@ -8927,14 +8697,12 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M115" t="n">
-        <v>15</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539918.html</t>
@@ -9001,14 +8769,12 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="M116" t="n">
         <v>9</v>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539917.html</t>
@@ -9075,14 +8841,12 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M117" t="n">
         <v>18</v>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539916.html</t>
@@ -9149,14 +8913,12 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M118" t="n">
         <v>46</v>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539914.html</t>
@@ -9223,14 +8985,12 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="M119" t="n">
         <v>36</v>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539900.html</t>
@@ -9297,14 +9057,12 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="M120" t="n">
         <v>20</v>
       </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539899.html</t>
@@ -9371,14 +9129,12 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M121" t="n">
         <v>15</v>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539898.html</t>
@@ -9445,14 +9201,12 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="M122" t="n">
         <v>15</v>
       </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539897.html</t>
@@ -9519,14 +9273,12 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="M123" t="n">
         <v>12</v>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539891.html</t>
@@ -9593,14 +9345,12 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M124" t="n">
         <v>8</v>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539890.html</t>
@@ -9667,14 +9417,12 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="M125" t="n">
         <v>5</v>
       </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szrzyhghj/202304/t20230410_539889.html</t>
@@ -9741,14 +9489,12 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M126" t="n">
         <v>7</v>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539884.html</t>
@@ -9815,14 +9561,12 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="M127" t="n">
         <v>2</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539882.html</t>
@@ -9889,14 +9633,12 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539880.html</t>
@@ -9963,14 +9705,12 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539875.html</t>
@@ -10037,14 +9777,12 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="M130" t="n">
         <v>5</v>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539870.html</t>
@@ -10111,14 +9849,12 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="M131" t="n">
         <v>10</v>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539867.html</t>
@@ -10185,14 +9921,12 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M132" t="n">
         <v>4</v>
       </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539864.html</t>
@@ -10259,14 +9993,12 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M133" t="n">
         <v>7</v>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539863.html</t>
@@ -10333,14 +10065,12 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M134" t="n">
         <v>36</v>
       </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjtysj/202304/t20230410_539858.html</t>
@@ -10407,14 +10137,12 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="M135" t="n">
         <v>82</v>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230410_539843.html</t>
@@ -10481,14 +10209,12 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M136" t="n">
         <v>52</v>
       </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230410_539842.html</t>
@@ -10555,14 +10281,12 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="M137" t="n">
         <v>128</v>
       </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230410_539836.html</t>
@@ -10629,14 +10353,12 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="M138" t="n">
         <v>57</v>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230410_539834.html</t>
@@ -10703,14 +10425,12 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M139" t="n">
         <v>212</v>
       </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/ssthjj/202304/t20230410_539824.html</t>
@@ -10777,14 +10497,12 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M140" t="n">
         <v>13</v>
       </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230410_539794.html</t>
@@ -10851,14 +10569,12 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M141" t="n">
         <v>11</v>
       </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230410_539789.html</t>
@@ -10925,14 +10641,12 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="M142" t="n">
         <v>3</v>
       </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230410_539786.html</t>
@@ -10999,14 +10713,12 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M143" t="n">
         <v>6</v>
       </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230410_539784.html</t>
@@ -11073,14 +10785,12 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="M144" t="n">
         <v>9</v>
       </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sgzw/202304/t20230410_539781.html</t>
@@ -11147,14 +10857,12 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M145" t="n">
         <v>11</v>
       </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539694.html</t>
@@ -11221,14 +10929,12 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="M146" t="n">
         <v>10</v>
       </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539691.html</t>
@@ -11295,14 +11001,12 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="M147" t="n">
         <v>16</v>
       </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539689.html</t>
@@ -11369,14 +11073,12 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="M148" t="n">
         <v>6</v>
       </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539680.html</t>
@@ -11443,14 +11145,12 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="M149" t="n">
         <v>5</v>
       </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539673.html</t>
@@ -11517,14 +11217,12 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="M150" t="n">
         <v>6</v>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539669.html</t>
@@ -11591,14 +11289,12 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="M151" t="n">
         <v>11</v>
       </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/skjj/202304/t20230410_539622.html</t>
@@ -11618,32 +11314,32 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>鄂州市2021年主要商品价格运行概况</t>
+          <t>鄂州市各类市场主体发展情况</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>生活服务</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>鄂州市2021年主要商品价格运行概况</t>
+          <t>鄂州市各类市场主体发展情况</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>鄂州市发展和改革委员会</t>
+          <t>鄂州市市场监督管理局</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11652,7 +11348,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -11665,17 +11361,15 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>359</v>
+        <v>600</v>
       </c>
       <c r="M152" t="n">
-        <v>15</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539205.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/scjdglj/202304/t20230407_539226.html</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -11692,7 +11386,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>鄂州市场疫情期间主副食品，防控相关药品、用品价格监测一日一报</t>
+          <t>鄂州市2021年主要商品价格运行概况</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11702,7 +11396,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>鄂州市场疫情期间主副食品，防控相关药品、用品价格监测一日一报</t>
+          <t>鄂州市2021年主要商品价格运行概况</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -11712,12 +11406,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11739,17 +11433,15 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>155</v>
+        <v>372</v>
       </c>
       <c r="M153" t="n">
-        <v>3</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539203.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539205.html</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -11766,7 +11458,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>鄂州市静态管理期间价格监测周报</t>
+          <t>鄂州市场疫情期间主副食品，防控相关药品、用品价格监测一日一报</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11776,7 +11468,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>鄂州市静态管理期间价格监测周报</t>
+          <t>鄂州市场疫情期间主副食品，防控相关药品、用品价格监测一日一报</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11786,12 +11478,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11813,17 +11505,15 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1920</v>
+        <v>173</v>
       </c>
       <c r="M154" t="n">
-        <v>4</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539201.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539203.html</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -11840,32 +11530,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2021年分地区结构性投资完成情况</t>
+          <t>鄂州市静态管理期间价格监测周报</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>生活服务</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2021年分地区结构性投资完成情况</t>
+          <t>鄂州市静态管理期间价格监测周报</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>鄂州市经济和信息化局</t>
+          <t>鄂州市发展和改革委员会</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11887,17 +11577,15 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>45</v>
+        <v>1931</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
-      </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539166.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sfgw/202304/t20230407_539201.html</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -11914,7 +11602,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>全市工业技改投资同比增长</t>
+          <t>2021年分地区结构性投资完成情况</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11924,7 +11612,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>全市工业技改投资同比增长</t>
+          <t>2021年分地区结构性投资完成情况</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11934,12 +11622,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11948,30 +11636,28 @@
         </is>
       </c>
       <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>56</v>
+      </c>
+      <c r="M156" t="n">
         <v>2</v>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="L156" t="n">
-        <v>88</v>
-      </c>
-      <c r="M156" t="n">
-        <v>6</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539164.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539166.html</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -11988,17 +11674,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>全市工业运行情况简析</t>
+          <t>全市工业技改投资同比增长</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>工业农业</t>
+          <t>经济建设</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>全市工业运行情况简析</t>
+          <t>全市工业技改投资同比增长</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -12008,12 +11694,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12035,17 +11721,15 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M157" t="n">
-        <v>34</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539160.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539164.html</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -12062,17 +11746,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>全市2020年工业经济运行情况</t>
+          <t>全市工业运行情况简析</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>工业农业</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>全市2020年工业经济运行情况</t>
+          <t>全市工业运行情况简析</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -12082,12 +11766,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12096,7 +11780,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -12109,17 +11793,15 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539154.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539160.html</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -12136,17 +11818,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>鄂州市5G通信基础设施2020年9月份建设情况</t>
+          <t>全市2020年工业经济运行情况</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>公共安全</t>
+          <t>经济建设</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>鄂州市5G通信基础设施2020年9月份建设情况</t>
+          <t>全市2020年工业经济运行情况</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -12156,12 +11838,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12183,17 +11865,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>106</v>
-      </c>
-      <c r="M159" t="n">
-        <v>3</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539120.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539154.html</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -12210,17 +11888,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>鄂州市2020-2021年度5G产业发展专项资金拟奖补情况表</t>
+          <t>鄂州市5G通信基础设施2020年9月份建设情况</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>科技创新</t>
+          <t>公共安全</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>鄂州市2020-2021年度5G产业发展专项资金拟奖补情况表</t>
+          <t>鄂州市5G通信基础设施2020年9月份建设情况</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -12230,12 +11908,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12257,17 +11935,15 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M160" t="n">
-        <v>6</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539116.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539120.html</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -12284,32 +11960,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>农村劳动力外出从业情况简析</t>
+          <t>鄂州市2020-2021年度5G产业发展专项资金拟奖补情况表</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>科技创新</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>农村劳动力外出从业情况简析</t>
+          <t>鄂州市2020-2021年度5G产业发展专项资金拟奖补情况表</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>鄂州市统计局</t>
+          <t>鄂州市经济和信息化局</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12331,17 +12007,15 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539105.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/sjxj/202304/t20230407_539116.html</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -12358,7 +12032,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2021年前三季度鄂州“四上”单位从业人员工资总额增长7.0%</t>
+          <t>农村劳动力外出从业情况简析</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12368,7 +12042,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2021年前三季度鄂州“四上”单位从业人员工资总额增长7.0%</t>
+          <t>农村劳动力外出从业情况简析</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12378,12 +12052,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12405,17 +12079,15 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539103.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539105.html</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -12432,17 +12104,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>鄂州市金融业运行情况</t>
+          <t>2021年前三季度鄂州“四上”单位从业人员工资总额增长7.0%</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>财税金融</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>鄂州市金融业运行情况</t>
+          <t>2021年前三季度鄂州“四上”单位从业人员工资总额增长7.0%</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -12452,12 +12124,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12466,7 +12138,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -12479,17 +12151,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>46</v>
-      </c>
-      <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="n">
-        <v>0</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539098.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539103.html</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -12506,17 +12174,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>全市消费品市场运行情况</t>
+          <t>鄂州市金融业运行情况</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>生活服务</t>
+          <t>财税金融</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>全市消费品市场运行情况</t>
+          <t>鄂州市金融业运行情况</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -12526,12 +12194,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12540,7 +12208,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -12553,17 +12221,15 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1921</v>
+        <v>52</v>
       </c>
       <c r="M164" t="n">
-        <v>13</v>
-      </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539091.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539098.html</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -12580,7 +12246,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>鄂州市社会消费品零售总额同比增长</t>
+          <t>全市消费品市场运行情况</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -12590,7 +12256,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>鄂州市社会消费品零售总额同比增长</t>
+          <t>全市消费品市场运行情况</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -12600,12 +12266,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -12614,7 +12280,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -12627,17 +12293,15 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1911</v>
+        <v>1932</v>
       </c>
       <c r="M165" t="n">
-        <v>7</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539089.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539091.html</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -12654,7 +12318,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>鄂州全社会用电量同比增长</t>
+          <t>鄂州市社会消费品零售总额同比增长</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -12664,7 +12328,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>鄂州全社会用电量同比增长</t>
+          <t>鄂州市社会消费品零售总额同比增长</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12674,12 +12338,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12701,17 +12365,15 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1870</v>
+        <v>1923</v>
       </c>
       <c r="M166" t="n">
-        <v>2</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539085.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539089.html</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -12728,17 +12390,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>鄂州固定资产投资增长</t>
+          <t>鄂州全社会用电量同比增长</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>生活服务</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>鄂州固定资产投资增长</t>
+          <t>鄂州全社会用电量同比增长</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -12748,12 +12410,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12762,7 +12424,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -12775,17 +12437,15 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>49</v>
+        <v>1879</v>
       </c>
       <c r="M167" t="n">
-        <v>1</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539084.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539085.html</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -12802,17 +12462,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>鄂州市国民经济和社会发展统计公报</t>
+          <t>鄂州固定资产投资增长</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>社会发展</t>
+          <t>经济建设</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>鄂州市国民经济和社会发展统计公报</t>
+          <t>鄂州固定资产投资增长</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12822,12 +12482,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12836,7 +12496,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -12849,17 +12509,15 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>324</v>
+        <v>57</v>
       </c>
       <c r="M168" t="n">
-        <v>126</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539080.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539084.html</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -12876,17 +12534,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>鄂州市经济运行情况简析</t>
+          <t>鄂州市国民经济和社会发展统计公报</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>社会发展</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>鄂州市经济运行情况简析</t>
+          <t>鄂州市国民经济和社会发展统计公报</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12896,12 +12554,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12910,7 +12568,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -12923,17 +12581,15 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>126</v>
+        <v>349</v>
       </c>
       <c r="M169" t="n">
-        <v>53</v>
-      </c>
-      <c r="N169" t="n">
-        <v>0</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539078.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539080.html</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -12950,7 +12606,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>鄂州市工业经济运行情况简析</t>
+          <t>鄂州市经济运行情况简析</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -12960,7 +12616,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>鄂州市工业经济运行情况简析</t>
+          <t>鄂州市经济运行情况简析</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -12970,12 +12626,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12984,7 +12640,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -12997,17 +12653,15 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="M170" t="n">
-        <v>11</v>
-      </c>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539069.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539078.html</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -13024,7 +12678,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>鄂州规上文化企业营业收入增长</t>
+          <t>鄂州市工业经济运行情况简析</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -13034,7 +12688,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>鄂州规上文化企业营业收入增长</t>
+          <t>鄂州市工业经济运行情况简析</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -13044,12 +12698,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13058,7 +12712,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -13071,17 +12725,15 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M171" t="n">
-        <v>5</v>
-      </c>
-      <c r="N171" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_538980.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_539069.html</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -13098,32 +12750,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>鄂州市住房租赁补贴发放情况</t>
+          <t>鄂州规上文化企业营业收入增长</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>城建住房</t>
+          <t>经济建设</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>鄂州市住房租赁补贴发放情况</t>
+          <t>鄂州规上文化企业营业收入增长</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>鄂州市住房和城乡建设局</t>
+          <t>鄂州市统计局</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13132,7 +12784,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -13145,17 +12797,15 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="M172" t="n">
-        <v>17</v>
-      </c>
-      <c r="N172" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538900.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/stjj/202304/t20230407_538980.html</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -13172,7 +12822,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>鄂州市低保、低收入家庭住房租赁补贴发放花名册</t>
+          <t>鄂州市住房租赁补贴发放情况</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -13182,7 +12832,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>鄂州市低保、低收入家庭住房租赁补贴发放花名册</t>
+          <t>鄂州市住房租赁补贴发放情况</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -13192,12 +12842,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13206,7 +12856,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -13219,17 +12869,15 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>977</v>
+        <v>135</v>
       </c>
       <c r="M173" t="n">
-        <v>35</v>
-      </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538899.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538900.html</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -13246,7 +12894,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>低保、低收入无房家庭申请公租房配租公示</t>
+          <t>鄂州市低保、低收入家庭住房租赁补贴发放花名册</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13256,7 +12904,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>低保、低收入无房家庭申请公租房配租公示</t>
+          <t>鄂州市低保、低收入家庭住房租赁补贴发放花名册</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -13266,12 +12914,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13280,7 +12928,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -13293,17 +12941,15 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>957</v>
+        <v>991</v>
       </c>
       <c r="M174" t="n">
-        <v>8</v>
-      </c>
-      <c r="N174" t="n">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538895.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538899.html</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -13320,7 +12966,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>鄂州市公租房配租及租赁补贴领取资格确认汇总表</t>
+          <t>低保、低收入无房家庭申请公租房配租公示</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13330,7 +12976,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>鄂州市公租房配租及租赁补贴领取资格确认汇总表</t>
+          <t>低保、低收入无房家庭申请公租房配租公示</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -13340,12 +12986,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13354,7 +13000,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -13367,17 +13013,15 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>923</v>
+        <v>964</v>
       </c>
       <c r="M175" t="n">
-        <v>5</v>
-      </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538893.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538895.html</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -13394,7 +13038,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>城镇住房困难家庭住房保障公示明细表</t>
+          <t>鄂州市公租房配租及租赁补贴领取资格确认汇总表</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -13404,7 +13048,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>城镇住房困难家庭住房保障公示明细表</t>
+          <t>鄂州市公租房配租及租赁补贴领取资格确认汇总表</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -13414,12 +13058,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13428,7 +13072,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -13441,17 +13085,15 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="M176" t="n">
-        <v>10</v>
-      </c>
-      <c r="N176" t="n">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
-          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538884.html</t>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538893.html</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -13468,67 +13110,137 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
+          <t>城镇住房困难家庭住房保障公示明细表</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>城建住房</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>城镇住房困难家庭住房保障公示明细表</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>鄂州市住房和城乡建设局</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>一般公开</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>957</v>
+      </c>
+      <c r="M177" t="n">
+        <v>10</v>
+      </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538884.html</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>按需更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>鄂州市</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
           <t>鄂州市房地产市场运行情况</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>城建住房</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>鄂州市房地产市场运行情况</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>鄂州市住房和城乡建设局</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>一般公开</t>
-        </is>
-      </c>
-      <c r="I177" t="n">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>一般公开</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
         <v>20</v>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="L177" t="n">
-        <v>1239</v>
-      </c>
-      <c r="M177" t="n">
-        <v>162</v>
-      </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" t="inlineStr">
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1270</v>
+      </c>
+      <c r="M178" t="n">
+        <v>165</v>
+      </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
         <is>
           <t>https://www.ezhou.gov.cn/sjkfn/sjj/bmfl/szjj/202304/t20230407_538871.html</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr">
+      <c r="P178" t="inlineStr">
         <is>
           <t>按需更新</t>
         </is>
